--- a/sheets/대금율보/검수/님은 먼곳에.xlsx
+++ b/sheets/대금율보/검수/님은 먼곳에.xlsx
@@ -4814,8 +4814,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶋
-‹</t>
+          <t xml:space="preserve">㶋</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -4952,7 +4951,6 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 汰</t>
         </is>
       </c>
@@ -4986,7 +4984,6 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潢</t>
         </is>
       </c>
@@ -5117,8 +5114,7 @@
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰汰
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="M9" s="23"/>
@@ -5332,7 +5328,6 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潕</t>
         </is>
       </c>
@@ -5355,7 +5350,6 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 汰</t>
         </is>
       </c>
@@ -5406,8 +5400,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
-‹</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -5487,8 +5480,7 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–淋
-‹</t>
+–淋</t>
         </is>
       </c>
       <c r="M17" s="23"/>
@@ -5722,7 +5714,6 @@
       <c r="D22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潢</t>
         </is>
       </c>
@@ -5767,7 +5758,6 @@
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 湳</t>
         </is>
       </c>
@@ -5830,17 +5820,9 @@
       <c r="C24" s="23"/>
       <c r="D24" s="21"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F24" s="21"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H24" s="21"/>
       <c r="I24" s="23"/>
       <c r="J24" s="21"/>
       <c r="K24" s="23"/>

--- a/sheets/대금율보/검수/님은 먼곳에.xlsx
+++ b/sheets/대금율보/검수/님은 먼곳에.xlsx
@@ -4737,24 +4737,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.43" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.43" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="M18" s="28"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="63.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="63.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5829,7 +5829,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="63.43" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -5854,7 +5854,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="63.43" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -5889,6 +5889,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
 </worksheet>
 </file>